--- a/sesion-07/Laboratorio_S07.xlsx
+++ b/sesion-07/Laboratorio_S07.xlsx
@@ -276,7 +276,7 @@
     <t xml:space="preserve">Parte 3 · Lista de EDA rápida</t>
   </si>
   <si>
-    <t xml:space="preserve">El barrido que se le hace a cualquier registro antes de calcular nada.</t>
+    <t xml:space="preserve">El barrido sobre el mismo padrón (hoja Depuración), antes de calcular nada.</t>
   </si>
   <si>
     <t xml:space="preserve">Pregunta de EDA</t>
